--- a/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_10_APM_DF.xlsx
+++ b/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_10_APM_DF.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
   <si>
     <t>Run</t>
   </si>
@@ -33,16 +33,28 @@
     <t>Seed</t>
   </si>
   <si>
-    <t>PathfindingTime_s</t>
+    <t>InitialPathfindingTime_s</t>
+  </si>
+  <si>
+    <t>IncrementalPathfindingTime_s</t>
   </si>
   <si>
     <t>SimulationTime_s</t>
   </si>
   <si>
+    <t>Total TL</t>
+  </si>
+  <si>
     <t>Number of runs</t>
   </si>
   <si>
-    <t>Average pathfinding time (s)</t>
+    <t>Average initial pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average incremental pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average total pathfinding time (s)</t>
   </si>
   <si>
     <t>Average simulation time (s)</t>
@@ -397,10 +409,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,729 +425,1051 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1.0</v>
       </c>
       <c r="B2">
-        <v>2.479329582e9</v>
+        <v>9.7503157e7</v>
       </c>
       <c r="C2">
-        <v>46.8438831</v>
+        <v>41.510707399999994</v>
       </c>
       <c r="D2">
-        <v>1.5054436</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>430.51347870000006</v>
+      </c>
+      <c r="E2">
+        <v>1.256233900000002</v>
+      </c>
+      <c r="F2">
+        <v>9.160000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2.0</v>
       </c>
       <c r="B3">
-        <v>3.229426941e9</v>
+        <v>2.749801108e9</v>
       </c>
       <c r="C3">
-        <v>43.633307900000005</v>
+        <v>38.557291</v>
       </c>
       <c r="D3">
-        <v>0.0112626</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>426.69385900000003</v>
+      </c>
+      <c r="E3">
+        <v>0.010870500000000007</v>
+      </c>
+      <c r="F3">
+        <v>7.320000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3.0</v>
       </c>
       <c r="B4">
-        <v>1.697135936e9</v>
+        <v>3.306271858e9</v>
       </c>
       <c r="C4">
-        <v>41.7223712</v>
+        <v>37.909732299999995</v>
       </c>
       <c r="D4">
-        <v>0.0108197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>425.0262606</v>
+      </c>
+      <c r="E4">
+        <v>0.018057900000000026</v>
+      </c>
+      <c r="F4">
+        <v>5.955000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4.0</v>
       </c>
       <c r="B5">
-        <v>3.738714219e9</v>
+        <v>1.864036382e9</v>
       </c>
       <c r="C5">
-        <v>43.078299200000004</v>
+        <v>38.3276238</v>
       </c>
       <c r="D5">
-        <v>0.010811</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>426.09426829999995</v>
+      </c>
+      <c r="E5">
+        <v>0.01106320000000002</v>
+      </c>
+      <c r="F5">
+        <v>9.625000000000009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5.0</v>
       </c>
       <c r="B6">
-        <v>2.226009881e9</v>
+        <v>1.16426881e9</v>
       </c>
       <c r="C6">
-        <v>44.948339999999995</v>
+        <v>38.8423729</v>
       </c>
       <c r="D6">
-        <v>0.0106415</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>429.56320819999996</v>
+      </c>
+      <c r="E6">
+        <v>0.011525100000000009</v>
+      </c>
+      <c r="F6">
+        <v>7.000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6.0</v>
       </c>
       <c r="B7">
-        <v>2.125487893e9</v>
+        <v>4.275950348e9</v>
       </c>
       <c r="C7">
-        <v>40.4292182</v>
+        <v>38.4497585</v>
       </c>
       <c r="D7">
-        <v>0.011313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>428.3468754</v>
+      </c>
+      <c r="E7">
+        <v>0.011837199999999996</v>
+      </c>
+      <c r="F7">
+        <v>9.320000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7.0</v>
       </c>
       <c r="B8">
-        <v>3.429786748e9</v>
+        <v>1.540047515e9</v>
       </c>
       <c r="C8">
-        <v>42.3016059</v>
+        <v>38.5388863</v>
       </c>
       <c r="D8">
-        <v>0.0112347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>426.3098565</v>
+      </c>
+      <c r="E8">
+        <v>0.011060000000000004</v>
+      </c>
+      <c r="F8">
+        <v>4.160000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8.0</v>
       </c>
       <c r="B9">
-        <v>2.2275544e9</v>
+        <v>2.446773351e9</v>
       </c>
       <c r="C9">
-        <v>43.8123481</v>
+        <v>38.8464682</v>
       </c>
       <c r="D9">
-        <v>0.0130942</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>428.1931927999999</v>
+      </c>
+      <c r="E9">
+        <v>0.011288700000000026</v>
+      </c>
+      <c r="F9">
+        <v>6.7950000000000035</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9.0</v>
       </c>
       <c r="B10">
-        <v>1.277256792e9</v>
+        <v>4.002996553e9</v>
       </c>
       <c r="C10">
-        <v>42.907361900000005</v>
+        <v>37.5177444</v>
       </c>
       <c r="D10">
-        <v>0.0175498</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>428.5619929</v>
+      </c>
+      <c r="E10">
+        <v>0.010835200000000017</v>
+      </c>
+      <c r="F10">
+        <v>6.645000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10.0</v>
       </c>
       <c r="B11">
-        <v>1.851015455e9</v>
+        <v>3.718695017e9</v>
       </c>
       <c r="C11">
-        <v>40.633437400000005</v>
+        <v>38.4564665</v>
       </c>
       <c r="D11">
-        <v>0.0117563</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>427.9356944</v>
+      </c>
+      <c r="E11">
+        <v>0.011368000000000026</v>
+      </c>
+      <c r="F11">
+        <v>6.875000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11.0</v>
       </c>
       <c r="B12">
-        <v>1.05986468e9</v>
+        <v>1.735958121e9</v>
       </c>
       <c r="C12">
-        <v>42.9855623</v>
+        <v>38.6240785</v>
       </c>
       <c r="D12">
-        <v>0.0257593</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>427.8479343</v>
+      </c>
+      <c r="E12">
+        <v>0.017200099999999992</v>
+      </c>
+      <c r="F12">
+        <v>5.845000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12.0</v>
       </c>
       <c r="B13">
-        <v>1.026901666e9</v>
+        <v>1.625050769e9</v>
       </c>
       <c r="C13">
-        <v>41.4499878</v>
+        <v>37.554216499999995</v>
       </c>
       <c r="D13">
-        <v>0.0111509</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>425.98798819999996</v>
+      </c>
+      <c r="E13">
+        <v>0.011473000000000011</v>
+      </c>
+      <c r="F13">
+        <v>8.025000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13.0</v>
       </c>
       <c r="B14">
-        <v>9.76758869e8</v>
+        <v>4.041863286e9</v>
       </c>
       <c r="C14">
-        <v>41.7975715</v>
+        <v>38.7202189</v>
       </c>
       <c r="D14">
-        <v>0.017811</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>427.6475713</v>
+      </c>
+      <c r="E14">
+        <v>0.011003600000000018</v>
+      </c>
+      <c r="F14">
+        <v>4.9650000000000025</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14.0</v>
       </c>
       <c r="B15">
-        <v>3.266993983e9</v>
+        <v>1.439031495e9</v>
       </c>
       <c r="C15">
-        <v>40.5066105</v>
+        <v>38.5623498</v>
       </c>
       <c r="D15">
-        <v>0.0109554</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>2965.5611470000003</v>
+      </c>
+      <c r="E15">
+        <v>0.010793000000000018</v>
+      </c>
+      <c r="F15">
+        <v>8.080000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15.0</v>
       </c>
       <c r="B16">
-        <v>3.892646538e9</v>
+        <v>3.977000866e9</v>
       </c>
       <c r="C16">
-        <v>41.433270799999995</v>
+        <v>37.237137999999995</v>
       </c>
       <c r="D16">
-        <v>0.0107775</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>421.61391060000005</v>
+      </c>
+      <c r="E16">
+        <v>0.010825000000000003</v>
+      </c>
+      <c r="F16">
+        <v>9.530000000000008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16.0</v>
       </c>
       <c r="B17">
-        <v>3.00453414e9</v>
+        <v>2.435724005e9</v>
       </c>
       <c r="C17">
-        <v>40.2108136</v>
+        <v>37.999754</v>
       </c>
       <c r="D17">
-        <v>0.0116987</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>422.4628209</v>
+      </c>
+      <c r="E17">
+        <v>0.011039200000000029</v>
+      </c>
+      <c r="F17">
+        <v>6.8000000000000025</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17.0</v>
       </c>
       <c r="B18">
-        <v>1.63518514e8</v>
+        <v>1.330140899e9</v>
       </c>
       <c r="C18">
-        <v>40.662188799999996</v>
+        <v>38.0010075</v>
       </c>
       <c r="D18">
-        <v>0.0128769</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>420.9861404</v>
+      </c>
+      <c r="E18">
+        <v>0.010751100000000017</v>
+      </c>
+      <c r="F18">
+        <v>6.505000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18.0</v>
       </c>
       <c r="B19">
-        <v>3.337207271e9</v>
+        <v>9.60977235e8</v>
       </c>
       <c r="C19">
-        <v>39.7910162</v>
+        <v>37.6962939</v>
       </c>
       <c r="D19">
-        <v>0.0117754</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>420.97312280000006</v>
+      </c>
+      <c r="E19">
+        <v>0.012326600000000024</v>
+      </c>
+      <c r="F19">
+        <v>7.890000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19.0</v>
       </c>
       <c r="B20">
-        <v>2.605808958e9</v>
+        <v>4.050709429e9</v>
       </c>
       <c r="C20">
-        <v>42.320035000000004</v>
+        <v>37.9421566</v>
       </c>
       <c r="D20">
-        <v>0.0107716</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>430.46767969999996</v>
+      </c>
+      <c r="E20">
+        <v>0.01090370000000001</v>
+      </c>
+      <c r="F20">
+        <v>7.540000000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20.0</v>
       </c>
       <c r="B21">
-        <v>1.23363152e8</v>
+        <v>3.034603354e9</v>
       </c>
       <c r="C21">
-        <v>40.9638676</v>
+        <v>38.0511659</v>
       </c>
       <c r="D21">
-        <v>0.0101949</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>421.8974981</v>
+      </c>
+      <c r="E21">
+        <v>0.011350900000000006</v>
+      </c>
+      <c r="F21">
+        <v>5.720000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21.0</v>
       </c>
       <c r="B22">
-        <v>2.814153822e9</v>
+        <v>2.867341977e9</v>
       </c>
       <c r="C22">
-        <v>39.7261588</v>
+        <v>37.2617088</v>
       </c>
       <c r="D22">
-        <v>0.0100132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>419.4305522</v>
+      </c>
+      <c r="E22">
+        <v>0.01078950000000002</v>
+      </c>
+      <c r="F22">
+        <v>10.625000000000009</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22.0</v>
       </c>
       <c r="B23">
-        <v>1.751200571e9</v>
+        <v>4.145164045e9</v>
       </c>
       <c r="C23">
-        <v>38.764716099999994</v>
+        <v>37.836002</v>
       </c>
       <c r="D23">
-        <v>0.0108692</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>421.22334349999994</v>
+      </c>
+      <c r="E23">
+        <v>0.01106370000000002</v>
+      </c>
+      <c r="F23">
+        <v>3.8850000000000025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23.0</v>
       </c>
       <c r="B24">
-        <v>4.074255516e9</v>
+        <v>3.319523008e9</v>
       </c>
       <c r="C24">
-        <v>39.8441367</v>
+        <v>38.0468057</v>
       </c>
       <c r="D24">
-        <v>0.0151709</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>421.2617941</v>
+      </c>
+      <c r="E24">
+        <v>0.010986300000000017</v>
+      </c>
+      <c r="F24">
+        <v>10.330000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24.0</v>
       </c>
       <c r="B25">
-        <v>2.237715506e9</v>
+        <v>3.395931646e9</v>
       </c>
       <c r="C25">
-        <v>38.9297925</v>
+        <v>37.142747199999995</v>
       </c>
       <c r="D25">
-        <v>0.0112052</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>420.6745011</v>
+      </c>
+      <c r="E25">
+        <v>0.010679400000000009</v>
+      </c>
+      <c r="F25">
+        <v>8.610000000000007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>25.0</v>
       </c>
       <c r="B26">
-        <v>2.200081577e9</v>
+        <v>3.807937199e9</v>
       </c>
       <c r="C26">
-        <v>39.648640799999995</v>
+        <v>37.898338700000004</v>
       </c>
       <c r="D26">
-        <v>0.0100609</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>421.34712809999996</v>
+      </c>
+      <c r="E26">
+        <v>0.01774310000000001</v>
+      </c>
+      <c r="F26">
+        <v>9.495000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>26.0</v>
       </c>
       <c r="B27">
-        <v>3.889545367e9</v>
+        <v>2.219112475e9</v>
       </c>
       <c r="C27">
-        <v>41.2731337</v>
+        <v>38.1931276</v>
       </c>
       <c r="D27">
-        <v>0.0111921</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>421.4387888</v>
+      </c>
+      <c r="E27">
+        <v>0.010677099999999995</v>
+      </c>
+      <c r="F27">
+        <v>3.6350000000000025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>27.0</v>
       </c>
       <c r="B28">
-        <v>6.88941985e8</v>
+        <v>1.122623423e9</v>
       </c>
       <c r="C28">
-        <v>41.4302861</v>
+        <v>37.150272</v>
       </c>
       <c r="D28">
-        <v>0.0114291</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>418.582899</v>
+      </c>
+      <c r="E28">
+        <v>0.010962700000000013</v>
+      </c>
+      <c r="F28">
+        <v>8.545000000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>28.0</v>
       </c>
       <c r="B29">
-        <v>3.426846063e9</v>
+        <v>1.384007565e9</v>
       </c>
       <c r="C29">
-        <v>39.270477299999996</v>
+        <v>38.3620286</v>
       </c>
       <c r="D29">
-        <v>0.0106557</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>420.9035662</v>
+      </c>
+      <c r="E29">
+        <v>0.010747700000000008</v>
+      </c>
+      <c r="F29">
+        <v>7.890000000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>29.0</v>
       </c>
       <c r="B30">
-        <v>4.193592696e9</v>
+        <v>2.445669533e9</v>
       </c>
       <c r="C30">
-        <v>40.400271399999994</v>
+        <v>38.154396899999995</v>
       </c>
       <c r="D30">
-        <v>0.0109513</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>421.1169959</v>
+      </c>
+      <c r="E30">
+        <v>0.010787600000000022</v>
+      </c>
+      <c r="F30">
+        <v>8.695000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>30.0</v>
       </c>
       <c r="B31">
-        <v>3.32282958e9</v>
+        <v>4.233233551e9</v>
       </c>
       <c r="C31">
-        <v>39.8481342</v>
+        <v>37.2772634</v>
       </c>
       <c r="D31">
-        <v>0.0108691</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>419.58177279999995</v>
+      </c>
+      <c r="E31">
+        <v>0.011194900000000032</v>
+      </c>
+      <c r="F31">
+        <v>7.4500000000000055</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>31.0</v>
       </c>
       <c r="B32">
-        <v>2.126486225e9</v>
+        <v>1.566884336e9</v>
       </c>
       <c r="C32">
-        <v>40.2293098</v>
+        <v>38.1636315</v>
       </c>
       <c r="D32">
-        <v>0.0132319</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>420.9267255</v>
+      </c>
+      <c r="E32">
+        <v>0.010699000000000016</v>
+      </c>
+      <c r="F32">
+        <v>6.510000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>32.0</v>
       </c>
       <c r="B33">
-        <v>1.771144379e9</v>
+        <v>9.71378474e8</v>
       </c>
       <c r="C33">
-        <v>39.0505117</v>
+        <v>38.1076578</v>
       </c>
       <c r="D33">
-        <v>0.0111917</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>421.1984536</v>
+      </c>
+      <c r="E33">
+        <v>0.010963700000000009</v>
+      </c>
+      <c r="F33">
+        <v>5.9200000000000035</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>33.0</v>
       </c>
       <c r="B34">
-        <v>2.751625265e9</v>
+        <v>7.27414221e8</v>
       </c>
       <c r="C34">
-        <v>39.63674150000001</v>
+        <v>37.057223</v>
       </c>
       <c r="D34">
-        <v>0.0105783</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>419.8240241</v>
+      </c>
+      <c r="E34">
+        <v>0.010974700000000013</v>
+      </c>
+      <c r="F34">
+        <v>6.2100000000000035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>34.0</v>
       </c>
       <c r="B35">
-        <v>3.364639719e9</v>
+        <v>9.81845523e8</v>
       </c>
       <c r="C35">
-        <v>39.1153552</v>
+        <v>37.875983100000006</v>
       </c>
       <c r="D35">
-        <v>0.0108314</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>420.2685917</v>
+      </c>
+      <c r="E35">
+        <v>0.011218500000000018</v>
+      </c>
+      <c r="F35">
+        <v>6.460000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>35.0</v>
       </c>
       <c r="B36">
-        <v>1.641431291e9</v>
+        <v>2.499164246e9</v>
       </c>
       <c r="C36">
-        <v>39.7440838</v>
+        <v>38.0637762</v>
       </c>
       <c r="D36">
-        <v>0.0105081</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>420.9632204</v>
+      </c>
+      <c r="E36">
+        <v>0.010715800000000006</v>
+      </c>
+      <c r="F36">
+        <v>7.385000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>36.0</v>
       </c>
       <c r="B37">
-        <v>8.816508e7</v>
+        <v>1.731048727e9</v>
       </c>
       <c r="C37">
-        <v>38.8856827</v>
+        <v>37.143393499999995</v>
       </c>
       <c r="D37">
-        <v>0.0122011</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>419.9560493</v>
+      </c>
+      <c r="E37">
+        <v>0.010752200000000012</v>
+      </c>
+      <c r="F37">
+        <v>6.570000000000005</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>37.0</v>
       </c>
       <c r="B38">
-        <v>3.227054095e9</v>
+        <v>2.249540029e9</v>
       </c>
       <c r="C38">
-        <v>39.4474332</v>
+        <v>37.774771900000005</v>
       </c>
       <c r="D38">
-        <v>0.0190265</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>423.1810891</v>
+      </c>
+      <c r="E38">
+        <v>0.01084580000000001</v>
+      </c>
+      <c r="F38">
+        <v>5.265000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>38.0</v>
       </c>
       <c r="B39">
-        <v>4.001771573e9</v>
+        <v>1.925649941e9</v>
       </c>
       <c r="C39">
-        <v>38.857275300000005</v>
+        <v>38.189712</v>
       </c>
       <c r="D39">
-        <v>0.0105302</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>421.3865155</v>
+      </c>
+      <c r="E39">
+        <v>0.010964300000000022</v>
+      </c>
+      <c r="F39">
+        <v>7.2450000000000045</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>39.0</v>
       </c>
       <c r="B40">
-        <v>2.1665826e9</v>
+        <v>1.634016102e9</v>
       </c>
       <c r="C40">
-        <v>40.0869095</v>
+        <v>37.055902</v>
       </c>
       <c r="D40">
-        <v>0.0107078</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>420.03448349999996</v>
+      </c>
+      <c r="E40">
+        <v>0.010717100000000014</v>
+      </c>
+      <c r="F40">
+        <v>7.025000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>40.0</v>
       </c>
       <c r="B41">
-        <v>4.119465172e9</v>
+        <v>2.778060401e9</v>
       </c>
       <c r="C41">
-        <v>40.949549999999995</v>
+        <v>37.8279391</v>
       </c>
       <c r="D41">
-        <v>0.0137904</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>420.0048233</v>
+      </c>
+      <c r="E41">
+        <v>0.010511100000000015</v>
+      </c>
+      <c r="F41">
+        <v>6.585000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>41.0</v>
       </c>
       <c r="B42">
-        <v>4.239401065e9</v>
+        <v>3.458223448e9</v>
       </c>
       <c r="C42">
-        <v>41.8734946</v>
+        <v>38.111844</v>
       </c>
       <c r="D42">
-        <v>0.0190413</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>422.8427801</v>
+      </c>
+      <c r="E42">
+        <v>0.017570000000000034</v>
+      </c>
+      <c r="F42">
+        <v>8.700000000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>42.0</v>
       </c>
       <c r="B43">
-        <v>2.9392522e9</v>
+        <v>3.891310939e9</v>
       </c>
       <c r="C43">
-        <v>43.8604731</v>
+        <v>37.3381664</v>
       </c>
       <c r="D43">
-        <v>0.023489</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>419.3930001</v>
+      </c>
+      <c r="E43">
+        <v>0.010927400000000023</v>
+      </c>
+      <c r="F43">
+        <v>7.010000000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>43.0</v>
       </c>
       <c r="B44">
-        <v>3.944615682e9</v>
+        <v>1.116331697e9</v>
       </c>
       <c r="C44">
-        <v>42.502852600000004</v>
+        <v>38.2350092</v>
       </c>
       <c r="D44">
-        <v>0.0108363</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>422.3864367</v>
+      </c>
+      <c r="E44">
+        <v>0.010901800000000019</v>
+      </c>
+      <c r="F44">
+        <v>8.750000000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>44.0</v>
       </c>
       <c r="B45">
-        <v>1.050883866e9</v>
+        <v>2.756036228e9</v>
       </c>
       <c r="C45">
-        <v>41.2976122</v>
+        <v>38.272679100000005</v>
       </c>
       <c r="D45">
-        <v>0.0197085</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>422.1007509</v>
+      </c>
+      <c r="E45">
+        <v>0.017291999999999995</v>
+      </c>
+      <c r="F45">
+        <v>9.200000000000006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>45.0</v>
       </c>
       <c r="B46">
-        <v>8.53043858e8</v>
+        <v>8.07162693e8</v>
       </c>
       <c r="C46">
-        <v>41.8555325</v>
+        <v>37.4350114</v>
       </c>
       <c r="D46">
-        <v>0.0115588</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>421.16102340000003</v>
+      </c>
+      <c r="E46">
+        <v>0.010779200000000004</v>
+      </c>
+      <c r="F46">
+        <v>8.005000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>46.0</v>
       </c>
       <c r="B47">
-        <v>1.591328303e9</v>
+        <v>3.750761449e9</v>
       </c>
       <c r="C47">
-        <v>40.8784034</v>
+        <v>38.147080599999995</v>
       </c>
       <c r="D47">
-        <v>0.0118737</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>421.0784381</v>
+      </c>
+      <c r="E47">
+        <v>0.010925800000000017</v>
+      </c>
+      <c r="F47">
+        <v>8.910000000000007</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>47.0</v>
       </c>
       <c r="B48">
-        <v>2.068968067e9</v>
+        <v>3.096899621e9</v>
       </c>
       <c r="C48">
-        <v>41.9706562</v>
+        <v>38.4817616</v>
       </c>
       <c r="D48">
-        <v>0.0133136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>422.33972639999996</v>
+      </c>
+      <c r="E48">
+        <v>0.01059920000000002</v>
+      </c>
+      <c r="F48">
+        <v>7.7450000000000045</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>48.0</v>
       </c>
       <c r="B49">
-        <v>5.54175219e8</v>
+        <v>4.101289305e9</v>
       </c>
       <c r="C49">
-        <v>41.6282342</v>
+        <v>37.2057639</v>
       </c>
       <c r="D49">
-        <v>0.0267041</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>420.170146</v>
+      </c>
+      <c r="E49">
+        <v>0.011037700000000013</v>
+      </c>
+      <c r="F49">
+        <v>9.475000000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>49.0</v>
       </c>
       <c r="B50">
-        <v>1.937303635e9</v>
+        <v>1.300309943e9</v>
       </c>
       <c r="C50">
-        <v>41.7449079</v>
+        <v>37.778416899999996</v>
       </c>
       <c r="D50">
-        <v>0.0101793</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>420.18575780000003</v>
+      </c>
+      <c r="E50">
+        <v>0.010907900000000017</v>
+      </c>
+      <c r="F50">
+        <v>10.085000000000008</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>50.0</v>
       </c>
       <c r="B51">
-        <v>3.105388918e9</v>
+        <v>3.232070484e9</v>
       </c>
       <c r="C51">
-        <v>40.696721499999995</v>
+        <v>37.977359</v>
       </c>
       <c r="D51">
-        <v>0.0109296</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>421.86875069999996</v>
+      </c>
+      <c r="E51">
+        <v>0.010974300000000013</v>
+      </c>
+      <c r="F51">
+        <v>6.195000000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B53">
-        <v>41.11757170999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>38.01822408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B54">
-        <v>0.042806926</v>
+        <v>473.79033255999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55">
+        <v>511.80855663999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56">
+        <v>0.03655430800000006</v>
       </c>
     </row>
   </sheetData>
